--- a/jane-r9k5/Jane_My_Expressions.xlsx
+++ b/jane-r9k5/Jane_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -710,8 +710,140 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Back then, I was ~ing</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>그땐 ~하고 있었어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>I remember ~ing</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>~했던 게 기억나요</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Everyone was worried about ~</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>다들 ~를 걱정했죠</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>My guess is ~</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>제 추측엔 ~</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>It would take ~ to ~</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>~하려면 ~가 필요할 거예요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Class 4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>So that's why ~</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>그래서 ~인 거군요</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>